--- a/PTBR/Lang/PTBR/Game/KeyItem.xlsx
+++ b/PTBR/Lang/PTBR/Game/KeyItem.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Encanto Antigo</t>
+          <t>Amuleto Velho</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Um amuleto de aparência um tanto familiar feito de conchas desbotadas.</t>
+          <t>Um amuleto de aparência familiar, feito de conchas desbotadas.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mochila Gastada</t>
+          <t>Mochila Bem Gasta</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fragrance of Goddess </t>
+          <t>Fragrance of Goddess</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A suave fragrância remanescente da Deusa da Sorte. Acredita-se que atraia a Deusa dos Desejos.</t>
+          <t xml:space="preserve">A suave fragrância restante da Deusa da Sorte. Dizem que atrai a Deusa dos Desejos. </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -646,9 +646,9 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saliva contendo o poder mágico de uma forte bênção.
+          <t>Saliva contendo o poder mágico de uma bênção forte.
 [Efeito Passivo]
-Aumenta o poder dos desejos feitos em poços.</t>
+Amplifica o poder dos desejos feitos nos poços.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pedaço de Pena da Deusa</t>
+          <t>Fragmento de Pena da Deusa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Um pedaço de pena que caiu da asa da Deusa da Cura.</t>
+          <t>Um pedaço de pena caído da asa da Deusa da Cura.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>A chave para as profundezas da mina em Vernis.</t>
+          <t>A chave para as profundezas da mina de Vernis.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bracelete do Perdão</t>
+          <t>Pulseira do Perdão</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Um bracelete esfarrapado tecido com vinhas ressecadas.</t>
+          <t>Uma pulseira esfarrapada tecida de cipós secos.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Um frasco cheio de um líquido transparente borbulhante. Fede a corrupção.</t>
+          <t>Um frasco cheio de um líquido claro e borbulhante. Fede a corrupção.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Um frasco cheio de um líquido transparente borbulhante. Cheira a detergente.</t>
+          <t>Um frasco cheio de um líquido claro e borbulhante. Cheira a detergente.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Uma licença para Engenheiro de Iluminação. Possuí-la permite mudar livremente as cores das luzes.</t>
+          <t>Uma licença de Engenheiro de Iluminação. Possuí-la permite mudar livremente as cores das luzes.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Uma licença que permite aos aventureiros explorar as misteriosas ruínas antigas.</t>
+          <t>Uma licença que permite aventureiros explorarem as misteriosas ruínas antigas.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Licença de Aventuriero Avançado</t>
+          <t>Licença de Aventureiro Avançado</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Uma licença que certifica o portador como um aventureiro avançado, permitindo a aquisição de fama além dos limites usuais para aventureiros e resulta na geração de perigosos Nefias em Tyris.</t>
+          <t>Uma licença que certifica o portador como aventureiro avançado, permitindo adquirir fama além dos limites normais para aventureiros e resulta no surgimento de Nefias perigosas em Tyris.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Uma moeda que se diz trazer fortuna para seu possuidor.</t>
+          <t>Uma moeda que dizem trazer fortuna ao seu portador.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
